--- a/seizu/timetrial.xlsx
+++ b/seizu/timetrial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="目標タイム" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="記録" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="集計" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="本番の流れ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目標タイム" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記録" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本番の流れ" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -224,13 +224,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -254,7 +254,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -278,7 +278,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -330,7 +330,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -345,9 +345,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -5212,7 +5212,7 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>□　7枚すべて描き終わっているか（1枚でも未完成なら不合格）</t>
+          <t>□　図面6枚＋面積表＋記述、⑴〜⑻すべて描き終わっているか（1つでも未完成なら不合格）</t>
         </is>
       </c>
     </row>

--- a/seizu/timetrial.xlsx
+++ b/seizu/timetrial.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目標タイム" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記録" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本番の流れ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="目標タイム" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="記録" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="集計" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="本番の流れ" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -224,13 +224,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -254,7 +254,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -278,7 +278,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -330,7 +330,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -345,9 +345,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
